--- a/Quickfinsure_Bank_Policy_Cards.xlsx
+++ b/Quickfinsure_Bank_Policy_Cards.xlsx
@@ -1,43 +1,373 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/120435612014f931/Tài liệu/Important Sheet/Anitigravity Projects/Quickfinsure/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_3F12451216A80BE399152093C815A669B06F13AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47ADCCC5-9E99-47AD-887D-B7B1C3475FAD}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Bank Policies Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Eligibility &amp; Dynamic Rules" sheetId="2" r:id="rId2"/>
     <sheet name="CIBIL Rate Matrix" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="113">
+  <si>
+    <t>Sr No</t>
+  </si>
+  <si>
+    <t>Card ID</t>
+  </si>
+  <si>
+    <t>Bank Name</t>
+  </si>
+  <si>
+    <t>Bank Code</t>
+  </si>
+  <si>
+    <t>Loan Type</t>
+  </si>
+  <si>
+    <t>Base Interest Rate (% p.a.)</t>
+  </si>
+  <si>
+    <t>Max FOIR (%)</t>
+  </si>
+  <si>
+    <t>Min CIBIL</t>
+  </si>
+  <si>
+    <t>Max CIBIL</t>
+  </si>
+  <si>
+    <t>Min Monthly Income (₹)</t>
+  </si>
+  <si>
+    <t>Min Tenure (Months)</t>
+  </si>
+  <si>
+    <t>Max Tenure (Months)</t>
+  </si>
+  <si>
+    <t>Max Tenure (Years)</t>
+  </si>
+  <si>
+    <t>Min Loan Amount (₹)</t>
+  </si>
+  <si>
+    <t>Max Loan Amount (₹)</t>
+  </si>
+  <si>
+    <t>Processing Fee (%)</t>
+  </si>
+  <si>
+    <t>Processing Fee Flat (₹)</t>
+  </si>
+  <si>
+    <t>Turnaround Time (Days)</t>
+  </si>
+  <si>
+    <t>Allowed Income Types</t>
+  </si>
+  <si>
+    <t>Priority Weight</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Created At</t>
+  </si>
+  <si>
+    <t>Last Updated</t>
+  </si>
+  <si>
+    <t>bpc_00000001</t>
+  </si>
+  <si>
+    <t>HDFC Bank</t>
+  </si>
+  <si>
+    <t>HDFC</t>
+  </si>
+  <si>
+    <t>HOME_LOAN</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>SALARIED, SELF_EMPLOYED_PROFESSIONAL, SELF_EMPLOYED_BUSINESS</t>
+  </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
+  <si>
+    <t>2026-10-03T11:29:54.484Z</t>
+  </si>
+  <si>
+    <t>bpc_00000002</t>
+  </si>
+  <si>
+    <t>State Bank of India</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>0.35%</t>
+  </si>
+  <si>
+    <t>bpc_00000003</t>
+  </si>
+  <si>
+    <t>ICICI Bank</t>
+  </si>
+  <si>
+    <t>ICICI</t>
+  </si>
+  <si>
+    <t>PERSONAL_LOAN</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>SALARIED</t>
+  </si>
+  <si>
+    <t>bpc_00000004</t>
+  </si>
+  <si>
+    <t>Axis Bank</t>
+  </si>
+  <si>
+    <t>AXIS</t>
+  </si>
+  <si>
+    <t>1.75%</t>
+  </si>
+  <si>
+    <t>SALARIED, SELF_EMPLOYED_PROFESSIONAL</t>
+  </si>
+  <si>
+    <t>bpc_00000005</t>
+  </si>
+  <si>
+    <t>Bajaj Housing Finance</t>
+  </si>
+  <si>
+    <t>BAJAJ</t>
+  </si>
+  <si>
+    <t>SALARIED, SELF_EMPLOYED_BUSINESS, SELF_EMPLOYED_PROFESSIONAL</t>
+  </si>
+  <si>
+    <t>bpc_00000006</t>
+  </si>
+  <si>
+    <t>Tata Capital</t>
+  </si>
+  <si>
+    <t>TATA</t>
+  </si>
+  <si>
+    <t>BUSINESS_LOAN</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>SELF_EMPLOYED_BUSINESS, SELF_EMPLOYED_PROFESSIONAL</t>
+  </si>
+  <si>
+    <t>bpc_00000007</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Bank</t>
+  </si>
+  <si>
+    <t>KOTAK</t>
+  </si>
+  <si>
+    <t>LOAN_AGAINST_PROPERTY</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>1%</t>
+  </si>
+  <si>
+    <t>Min Age (Years)</t>
+  </si>
+  <si>
+    <t>Max Age (Years)</t>
+  </si>
+  <si>
+    <t>Min Work Experience (Months)</t>
+  </si>
+  <si>
+    <t>Min Business Vintage (Months)</t>
+  </si>
+  <si>
+    <t>Allowed Company Categories</t>
+  </si>
+  <si>
+    <t>Allowed Salary Modes</t>
+  </si>
+  <si>
+    <t>Location Tiers</t>
+  </si>
+  <si>
+    <t>Max FOIR Tier Override (%)</t>
+  </si>
+  <si>
+    <t>Special Features &amp; USPs</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SUPER_CAT_A, CAT_A, CAT_B, GOVT</t>
+  </si>
+  <si>
+    <t>BANK_TRANSFER</t>
+  </si>
+  <si>
+    <t>METRO, TIER_1, TIER_2</t>
+  </si>
+  <si>
+    <t>Instant In-Principle Sanction | Zero Prepayment Penalty on Floating Rate | Digital Document Upload</t>
+  </si>
+  <si>
+    <t>SUPER_CAT_A, CAT_A, CAT_B, CAT_C, GOVT</t>
+  </si>
+  <si>
+    <t>BANK_TRANSFER, CHEQUE</t>
+  </si>
+  <si>
+    <t>METRO, TIER_1, TIER_2, TIER_3</t>
+  </si>
+  <si>
+    <t>Lowest Processing Fee in Industry | Concession for Women Borrowers (-0.05%) | No Hidden Ledger Charges</t>
+  </si>
+  <si>
+    <t>SUPER_CAT_A, CAT_A, CAT_B</t>
+  </si>
+  <si>
+    <t>Disbursal within 24 Hours | Completely Paperless E-KYC | Flexible 12-84m Tenure (Up to 7 Yrs)</t>
+  </si>
+  <si>
+    <t>SUPER_CAT_A, CAT_A, CAT_B, CAT_C</t>
+  </si>
+  <si>
+    <t>Quick Approval for Cat A/B Corporates | Part-Payment Option Available | Flexible Tenure up to 7 Years</t>
+  </si>
+  <si>
+    <t>Highest FOIR Eligibility (up to 65%) | Top-Up Loan up to ₹1 Crore | Customised EMI Structuring</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>Unsecured Collateral-Free Sanction | Fast In-Principle Verification | Overdraft Facility Linked</t>
+  </si>
+  <si>
+    <t>High LTV up to 70% of Property Market Value | Residential &amp; Commercial Collateral Accepted</t>
+  </si>
+  <si>
+    <t>Tier Description</t>
+  </si>
+  <si>
+    <t>Interest Rate (% p.a.)</t>
+  </si>
+  <si>
+    <t>Super Prime Tier</t>
+  </si>
+  <si>
+    <t>Prime Tier</t>
+  </si>
+  <si>
+    <t>Standard Tier</t>
+  </si>
+  <si>
+    <t>SBI Regular Home Loan (750+ CIBIL)</t>
+  </si>
+  <si>
+    <t>SBI Band 2</t>
+  </si>
+  <si>
+    <t>SBI Band 3</t>
+  </si>
+  <si>
+    <t>Top Corporate Tier</t>
+  </si>
+  <si>
+    <t>Standard Salaried Tier</t>
+  </si>
+  <si>
+    <t>Entry Salaried Tier</t>
+  </si>
+  <si>
+    <t>Prime Personal Loan</t>
+  </si>
+  <si>
+    <t>Standard Personal Loan</t>
+  </si>
+  <si>
+    <t>Prime Housing Tier</t>
+  </si>
+  <si>
+    <t>Flexi Housing Tier</t>
+  </si>
+  <si>
+    <t>Standard Housing Tier</t>
+  </si>
+  <si>
+    <t>Prime Business Tier</t>
+  </si>
+  <si>
+    <t>Growth Business Tier</t>
+  </si>
+  <si>
+    <t>Prime LAP Tier</t>
+  </si>
+  <si>
+    <t>Standard LAP Tier</t>
+  </si>
+  <si>
+    <t>Regular LAP Tier</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -67,14 +397,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -398,120 +740,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W8"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
-    <col min="14" max="14" width="22.83203125" customWidth="1"/>
-    <col min="15" max="15" width="22.83203125" customWidth="1"/>
-    <col min="16" max="16" width="22.83203125" customWidth="1"/>
-    <col min="17" max="17" width="22.83203125" customWidth="1"/>
-    <col min="18" max="18" width="22.83203125" customWidth="1"/>
-    <col min="19" max="19" width="22.83203125" customWidth="1"/>
-    <col min="20" max="20" width="22.83203125" customWidth="1"/>
-    <col min="21" max="21" width="22.83203125" customWidth="1"/>
-    <col min="22" max="22" width="22.83203125" customWidth="1"/>
-    <col min="23" max="23" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.58203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.9140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="61.4140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="22.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Sr No</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Card ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Bank Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Bank Code</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Loan Type</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Base Interest Rate (% p.a.)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Max FOIR (%)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Min CIBIL</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Max CIBIL</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Min Monthly Income (₹)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Min Tenure (Months)</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Max Tenure (Months)</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Max Tenure (Years)</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Min Loan Amount (₹)</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Max Loan Amount (₹)</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Processing Fee (%)</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Processing Fee Flat (₹)</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Turnaround Time (Days)</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Allowed Income Types</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Priority Weight</v>
-      </c>
-      <c r="U1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="V1" t="str">
-        <v>Created At</v>
-      </c>
-      <c r="W1" t="str">
-        <v>Last Updated</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>bpc_00000001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>HDFC Bank</v>
-      </c>
-      <c r="D2" t="str">
-        <v>HDFC</v>
-      </c>
-      <c r="E2" t="str">
-        <v>HOME_LOAN</v>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
       </c>
       <c r="F2">
         <v>8.4</v>
@@ -534,8 +876,8 @@
       <c r="L2">
         <v>360</v>
       </c>
-      <c r="M2" t="str">
-        <v>30.0</v>
+      <c r="M2" t="s">
+        <v>27</v>
       </c>
       <c r="N2">
         <v>500000</v>
@@ -543,8 +885,8 @@
       <c r="O2">
         <v>100000000</v>
       </c>
-      <c r="P2" t="str">
-        <v>0.5%</v>
+      <c r="P2" t="s">
+        <v>28</v>
       </c>
       <c r="Q2">
         <v>3000</v>
@@ -552,37 +894,37 @@
       <c r="R2">
         <v>3</v>
       </c>
-      <c r="S2" t="str">
-        <v>SALARIED, SELF_EMPLOYED_PROFESSIONAL, SELF_EMPLOYED_BUSINESS</v>
+      <c r="S2" t="s">
+        <v>29</v>
       </c>
       <c r="T2">
         <v>10</v>
       </c>
-      <c r="U2" t="str">
-        <v>ACTIVE</v>
-      </c>
-      <c r="V2" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-      <c r="W2" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="U2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>bpc_00000002</v>
-      </c>
-      <c r="C3" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="D3" t="str">
-        <v>SBI</v>
-      </c>
-      <c r="E3" t="str">
-        <v>HOME_LOAN</v>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
       </c>
       <c r="F3">
         <v>8.5</v>
@@ -605,8 +947,8 @@
       <c r="L3">
         <v>360</v>
       </c>
-      <c r="M3" t="str">
-        <v>30.0</v>
+      <c r="M3" t="s">
+        <v>27</v>
       </c>
       <c r="N3">
         <v>300000</v>
@@ -614,8 +956,8 @@
       <c r="O3">
         <v>150000000</v>
       </c>
-      <c r="P3" t="str">
-        <v>0.35%</v>
+      <c r="P3" t="s">
+        <v>35</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -623,37 +965,37 @@
       <c r="R3">
         <v>5</v>
       </c>
-      <c r="S3" t="str">
-        <v>SALARIED, SELF_EMPLOYED_PROFESSIONAL, SELF_EMPLOYED_BUSINESS</v>
+      <c r="S3" t="s">
+        <v>29</v>
       </c>
       <c r="T3">
         <v>9</v>
       </c>
-      <c r="U3" t="str">
-        <v>ACTIVE</v>
-      </c>
-      <c r="V3" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-      <c r="W3" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="U3" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>bpc_00000003</v>
-      </c>
-      <c r="C4" t="str">
-        <v>ICICI Bank</v>
-      </c>
-      <c r="D4" t="str">
-        <v>ICICI</v>
-      </c>
-      <c r="E4" t="str">
-        <v>PERSONAL_LOAN</v>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
       </c>
       <c r="F4">
         <v>10.75</v>
@@ -676,8 +1018,8 @@
       <c r="L4">
         <v>84</v>
       </c>
-      <c r="M4" t="str">
-        <v>7.0</v>
+      <c r="M4" t="s">
+        <v>40</v>
       </c>
       <c r="N4">
         <v>50000</v>
@@ -685,8 +1027,8 @@
       <c r="O4">
         <v>4000000</v>
       </c>
-      <c r="P4" t="str">
-        <v>1.5%</v>
+      <c r="P4" t="s">
+        <v>41</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -694,37 +1036,37 @@
       <c r="R4">
         <v>1</v>
       </c>
-      <c r="S4" t="str">
-        <v>SALARIED</v>
+      <c r="S4" t="s">
+        <v>42</v>
       </c>
       <c r="T4">
         <v>8</v>
       </c>
-      <c r="U4" t="str">
-        <v>ACTIVE</v>
-      </c>
-      <c r="V4" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-      <c r="W4" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="U4" t="s">
+        <v>30</v>
+      </c>
+      <c r="V4" t="s">
+        <v>31</v>
+      </c>
+      <c r="W4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>bpc_00000004</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Axis Bank</v>
-      </c>
-      <c r="D5" t="str">
-        <v>AXIS</v>
-      </c>
-      <c r="E5" t="str">
-        <v>PERSONAL_LOAN</v>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
       </c>
       <c r="F5">
         <v>10.99</v>
@@ -747,8 +1089,8 @@
       <c r="L5">
         <v>84</v>
       </c>
-      <c r="M5" t="str">
-        <v>7.0</v>
+      <c r="M5" t="s">
+        <v>40</v>
       </c>
       <c r="N5">
         <v>50000</v>
@@ -756,8 +1098,8 @@
       <c r="O5">
         <v>3500000</v>
       </c>
-      <c r="P5" t="str">
-        <v>1.75%</v>
+      <c r="P5" t="s">
+        <v>46</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -765,37 +1107,37 @@
       <c r="R5">
         <v>2</v>
       </c>
-      <c r="S5" t="str">
-        <v>SALARIED, SELF_EMPLOYED_PROFESSIONAL</v>
+      <c r="S5" t="s">
+        <v>47</v>
       </c>
       <c r="T5">
         <v>7</v>
       </c>
-      <c r="U5" t="str">
-        <v>ACTIVE</v>
-      </c>
-      <c r="V5" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-      <c r="W5" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="U5" t="s">
+        <v>30</v>
+      </c>
+      <c r="V5" t="s">
+        <v>31</v>
+      </c>
+      <c r="W5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>bpc_00000005</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Bajaj Housing Finance</v>
-      </c>
-      <c r="D6" t="str">
-        <v>BAJAJ</v>
-      </c>
-      <c r="E6" t="str">
-        <v>HOME_LOAN</v>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
       </c>
       <c r="F6">
         <v>8.6</v>
@@ -818,8 +1160,8 @@
       <c r="L6">
         <v>360</v>
       </c>
-      <c r="M6" t="str">
-        <v>30.0</v>
+      <c r="M6" t="s">
+        <v>27</v>
       </c>
       <c r="N6">
         <v>1000000</v>
@@ -827,8 +1169,8 @@
       <c r="O6">
         <v>150000000</v>
       </c>
-      <c r="P6" t="str">
-        <v>0.5%</v>
+      <c r="P6" t="s">
+        <v>28</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -836,37 +1178,37 @@
       <c r="R6">
         <v>2</v>
       </c>
-      <c r="S6" t="str">
-        <v>SALARIED, SELF_EMPLOYED_BUSINESS, SELF_EMPLOYED_PROFESSIONAL</v>
+      <c r="S6" t="s">
+        <v>51</v>
       </c>
       <c r="T6">
         <v>8</v>
       </c>
-      <c r="U6" t="str">
-        <v>ACTIVE</v>
-      </c>
-      <c r="V6" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-      <c r="W6" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="U6" t="s">
+        <v>30</v>
+      </c>
+      <c r="V6" t="s">
+        <v>31</v>
+      </c>
+      <c r="W6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>bpc_00000006</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Tata Capital</v>
-      </c>
-      <c r="D7" t="str">
-        <v>TATA</v>
-      </c>
-      <c r="E7" t="str">
-        <v>BUSINESS_LOAN</v>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
       </c>
       <c r="F7">
         <v>14.5</v>
@@ -889,8 +1231,8 @@
       <c r="L7">
         <v>48</v>
       </c>
-      <c r="M7" t="str">
-        <v>4.0</v>
+      <c r="M7" t="s">
+        <v>56</v>
       </c>
       <c r="N7">
         <v>300000</v>
@@ -898,8 +1240,8 @@
       <c r="O7">
         <v>7500000</v>
       </c>
-      <c r="P7" t="str">
-        <v>2%</v>
+      <c r="P7" t="s">
+        <v>57</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -907,37 +1249,37 @@
       <c r="R7">
         <v>3</v>
       </c>
-      <c r="S7" t="str">
-        <v>SELF_EMPLOYED_BUSINESS, SELF_EMPLOYED_PROFESSIONAL</v>
+      <c r="S7" t="s">
+        <v>58</v>
       </c>
       <c r="T7">
         <v>7</v>
       </c>
-      <c r="U7" t="str">
-        <v>ACTIVE</v>
-      </c>
-      <c r="V7" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-      <c r="W7" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="U7" t="s">
+        <v>30</v>
+      </c>
+      <c r="V7" t="s">
+        <v>31</v>
+      </c>
+      <c r="W7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>bpc_00000007</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Kotak Mahindra Bank</v>
-      </c>
-      <c r="D8" t="str">
-        <v>KOTAK</v>
-      </c>
-      <c r="E8" t="str">
-        <v>LOAN_AGAINST_PROPERTY</v>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
       </c>
       <c r="F8">
         <v>9.25</v>
@@ -960,8 +1302,8 @@
       <c r="L8">
         <v>180</v>
       </c>
-      <c r="M8" t="str">
-        <v>15.0</v>
+      <c r="M8" t="s">
+        <v>63</v>
       </c>
       <c r="N8">
         <v>1000000</v>
@@ -969,8 +1311,8 @@
       <c r="O8">
         <v>50000000</v>
       </c>
-      <c r="P8" t="str">
-        <v>1%</v>
+      <c r="P8" t="s">
+        <v>64</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -978,101 +1320,103 @@
       <c r="R8">
         <v>4</v>
       </c>
-      <c r="S8" t="str">
-        <v>SALARIED, SELF_EMPLOYED_BUSINESS, SELF_EMPLOYED_PROFESSIONAL</v>
+      <c r="S8" t="s">
+        <v>51</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
-      <c r="U8" t="str">
-        <v>ACTIVE</v>
-      </c>
-      <c r="V8" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
-      </c>
-      <c r="W8" t="str">
-        <v>2026-10-03T11:29:54.484Z</v>
+      <c r="U8" t="s">
+        <v>30</v>
+      </c>
+      <c r="V8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W8"/>
+    <ignoredError sqref="A1:W8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.9140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="89.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Sr No</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Bank Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Bank Code</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Loan Type</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Min Age (Years)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Max Age (Years)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Min Work Experience (Months)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Min Business Vintage (Months)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Allowed Company Categories</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Allowed Salary Modes</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Location Tiers</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Max FOIR Tier Override (%)</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Special Features &amp; USPs</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>HDFC Bank</v>
-      </c>
-      <c r="C2" t="str">
-        <v>HDFC</v>
-      </c>
-      <c r="D2" t="str">
-        <v>HOME_LOAN</v>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
       </c>
       <c r="E2">
         <v>21</v>
@@ -1083,37 +1427,37 @@
       <c r="G2">
         <v>24</v>
       </c>
-      <c r="H2" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="I2" t="str">
-        <v>SUPER_CAT_A, CAT_A, CAT_B, GOVT</v>
-      </c>
-      <c r="J2" t="str">
-        <v>BANK_TRANSFER</v>
-      </c>
-      <c r="K2" t="str">
-        <v>METRO, TIER_1, TIER_2</v>
+      <c r="H2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
       </c>
       <c r="L2">
         <v>60</v>
       </c>
-      <c r="M2" t="str">
-        <v>Instant In-Principle Sanction | Zero Prepayment Penalty on Floating Rate | Digital Document Upload</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="M2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="C3" t="str">
-        <v>SBI</v>
-      </c>
-      <c r="D3" t="str">
-        <v>HOME_LOAN</v>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
       </c>
       <c r="E3">
         <v>18</v>
@@ -1124,37 +1468,37 @@
       <c r="G3">
         <v>12</v>
       </c>
-      <c r="H3" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="I3" t="str">
-        <v>SUPER_CAT_A, CAT_A, CAT_B, CAT_C, GOVT</v>
-      </c>
-      <c r="J3" t="str">
-        <v>BANK_TRANSFER, CHEQUE</v>
-      </c>
-      <c r="K3" t="str">
-        <v>METRO, TIER_1, TIER_2, TIER_3</v>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" t="s">
+        <v>81</v>
       </c>
       <c r="L3">
         <v>55</v>
       </c>
-      <c r="M3" t="str">
-        <v>Lowest Processing Fee in Industry | Concession for Women Borrowers (-0.05%) | No Hidden Ledger Charges</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="M3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>ICICI Bank</v>
-      </c>
-      <c r="C4" t="str">
-        <v>ICICI</v>
-      </c>
-      <c r="D4" t="str">
-        <v>PERSONAL_LOAN</v>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
       </c>
       <c r="E4">
         <v>23</v>
@@ -1165,37 +1509,37 @@
       <c r="G4">
         <v>24</v>
       </c>
-      <c r="H4" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="I4" t="str">
-        <v>SUPER_CAT_A, CAT_A, CAT_B</v>
-      </c>
-      <c r="J4" t="str">
-        <v>BANK_TRANSFER</v>
-      </c>
-      <c r="K4" t="str">
-        <v>METRO, TIER_1, TIER_2</v>
+      <c r="H4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" t="s">
+        <v>77</v>
       </c>
       <c r="L4">
         <v>50</v>
       </c>
-      <c r="M4" t="str">
-        <v>Disbursal within 24 Hours | Completely Paperless E-KYC | Flexible 12-84m Tenure (Up to 7 Yrs)</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="M4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Axis Bank</v>
-      </c>
-      <c r="C5" t="str">
-        <v>AXIS</v>
-      </c>
-      <c r="D5" t="str">
-        <v>PERSONAL_LOAN</v>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
       </c>
       <c r="E5">
         <v>21</v>
@@ -1206,37 +1550,37 @@
       <c r="G5">
         <v>12</v>
       </c>
-      <c r="H5" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="I5" t="str">
-        <v>SUPER_CAT_A, CAT_A, CAT_B, CAT_C</v>
-      </c>
-      <c r="J5" t="str">
-        <v>BANK_TRANSFER</v>
-      </c>
-      <c r="K5" t="str">
-        <v>METRO, TIER_1, TIER_2</v>
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" t="s">
+        <v>77</v>
       </c>
       <c r="L5">
         <v>55</v>
       </c>
-      <c r="M5" t="str">
-        <v>Quick Approval for Cat A/B Corporates | Part-Payment Option Available | Flexible Tenure up to 7 Years</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="M5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Bajaj Housing Finance</v>
-      </c>
-      <c r="C6" t="str">
-        <v>BAJAJ</v>
-      </c>
-      <c r="D6" t="str">
-        <v>HOME_LOAN</v>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
       </c>
       <c r="E6">
         <v>23</v>
@@ -1247,37 +1591,37 @@
       <c r="G6">
         <v>24</v>
       </c>
-      <c r="H6" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="I6" t="str">
-        <v>SUPER_CAT_A, CAT_A, CAT_B, CAT_C, GOVT</v>
-      </c>
-      <c r="J6" t="str">
-        <v>BANK_TRANSFER</v>
-      </c>
-      <c r="K6" t="str">
-        <v>METRO, TIER_1, TIER_2, TIER_3</v>
+      <c r="H6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" t="s">
+        <v>81</v>
       </c>
       <c r="L6">
         <v>65</v>
       </c>
-      <c r="M6" t="str">
-        <v>Highest FOIR Eligibility (up to 65%) | Top-Up Loan up to ₹1 Crore | Customised EMI Structuring</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="M6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>Tata Capital</v>
-      </c>
-      <c r="C7" t="str">
-        <v>TATA</v>
-      </c>
-      <c r="D7" t="str">
-        <v>BUSINESS_LOAN</v>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
       </c>
       <c r="E7">
         <v>25</v>
@@ -1285,40 +1629,40 @@
       <c r="F7">
         <v>65</v>
       </c>
-      <c r="G7" t="str">
-        <v>N/A</v>
+      <c r="G7" t="s">
+        <v>74</v>
       </c>
       <c r="H7">
         <v>36</v>
       </c>
-      <c r="I7" t="str">
-        <v>All</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Any</v>
-      </c>
-      <c r="K7" t="str">
-        <v>METRO, TIER_1, TIER_2</v>
+      <c r="I7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K7" t="s">
+        <v>77</v>
       </c>
       <c r="L7">
         <v>60</v>
       </c>
-      <c r="M7" t="str">
-        <v>Unsecured Collateral-Free Sanction | Fast In-Principle Verification | Overdraft Facility Linked</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="M7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>Kotak Mahindra Bank</v>
-      </c>
-      <c r="C8" t="str">
-        <v>KOTAK</v>
-      </c>
-      <c r="D8" t="str">
-        <v>LOAN_AGAINST_PROPERTY</v>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
       </c>
       <c r="E8">
         <v>23</v>
@@ -1326,99 +1670,101 @@
       <c r="F8">
         <v>65</v>
       </c>
-      <c r="G8" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H8" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="I8" t="str">
-        <v>All</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Any</v>
-      </c>
-      <c r="K8" t="str">
-        <v>METRO, TIER_1, TIER_2</v>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K8" t="s">
+        <v>77</v>
       </c>
       <c r="L8">
         <v>60</v>
       </c>
-      <c r="M8" t="str">
-        <v>High LTV up to 70% of Property Market Value | Residential &amp; Commercial Collateral Accepted</v>
+      <c r="M8" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M8"/>
+    <ignoredError sqref="A1:M8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.9140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Bank Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Bank Code</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Loan Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Tier Description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Min CIBIL</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Max CIBIL</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Interest Rate (% p.a.)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Max FOIR (%)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Processing Fee (%)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Min Loan Amount (₹)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Max Loan Amount (₹)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>HDFC Bank</v>
-      </c>
-      <c r="B2" t="str">
-        <v>HDFC</v>
-      </c>
-      <c r="C2" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Super Prime Tier</v>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>94</v>
       </c>
       <c r="E2">
         <v>800</v>
@@ -1442,18 +1788,18 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>HDFC Bank</v>
-      </c>
-      <c r="B3" t="str">
-        <v>HDFC</v>
-      </c>
-      <c r="C3" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Prime Tier</v>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>95</v>
       </c>
       <c r="E3">
         <v>750</v>
@@ -1462,7 +1808,7 @@
         <v>799</v>
       </c>
       <c r="G3">
-        <v>8.45</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="H3">
         <v>60</v>
@@ -1477,18 +1823,18 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>HDFC Bank</v>
-      </c>
-      <c r="B4" t="str">
-        <v>HDFC</v>
-      </c>
-      <c r="C4" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Standard Tier</v>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>96</v>
       </c>
       <c r="E4">
         <v>700</v>
@@ -1512,18 +1858,18 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="B5" t="str">
-        <v>SBI</v>
-      </c>
-      <c r="C5" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D5" t="str">
-        <v>SBI Regular Home Loan (750+ CIBIL)</v>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
       </c>
       <c r="E5">
         <v>750</v>
@@ -1547,18 +1893,18 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="B6" t="str">
-        <v>SBI</v>
-      </c>
-      <c r="C6" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D6" t="str">
-        <v>SBI Band 2</v>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
       </c>
       <c r="E6">
         <v>700</v>
@@ -1582,18 +1928,18 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="B7" t="str">
-        <v>SBI</v>
-      </c>
-      <c r="C7" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D7" t="str">
-        <v>SBI Band 3</v>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
       </c>
       <c r="E7">
         <v>650</v>
@@ -1617,18 +1963,18 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ICICI Bank</v>
-      </c>
-      <c r="B8" t="str">
-        <v>ICICI</v>
-      </c>
-      <c r="C8" t="str">
-        <v>PERSONAL_LOAN</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Top Corporate Tier</v>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
       </c>
       <c r="E8">
         <v>780</v>
@@ -1652,18 +1998,18 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>ICICI Bank</v>
-      </c>
-      <c r="B9" t="str">
-        <v>ICICI</v>
-      </c>
-      <c r="C9" t="str">
-        <v>PERSONAL_LOAN</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Standard Salaried Tier</v>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
       </c>
       <c r="E9">
         <v>740</v>
@@ -1687,18 +2033,18 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ICICI Bank</v>
-      </c>
-      <c r="B10" t="str">
-        <v>ICICI</v>
-      </c>
-      <c r="C10" t="str">
-        <v>PERSONAL_LOAN</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Entry Salaried Tier</v>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1722,18 +2068,18 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Axis Bank</v>
-      </c>
-      <c r="B11" t="str">
-        <v>AXIS</v>
-      </c>
-      <c r="C11" t="str">
-        <v>PERSONAL_LOAN</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Prime Personal Loan</v>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
       </c>
       <c r="E11">
         <v>750</v>
@@ -1757,18 +2103,18 @@
         <v>3500000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Axis Bank</v>
-      </c>
-      <c r="B12" t="str">
-        <v>AXIS</v>
-      </c>
-      <c r="C12" t="str">
-        <v>PERSONAL_LOAN</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Standard Personal Loan</v>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
       </c>
       <c r="E12">
         <v>700</v>
@@ -1792,18 +2138,18 @@
         <v>3500000</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Bajaj Housing Finance</v>
-      </c>
-      <c r="B13" t="str">
-        <v>BAJAJ</v>
-      </c>
-      <c r="C13" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Prime Housing Tier</v>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>105</v>
       </c>
       <c r="E13">
         <v>750</v>
@@ -1827,18 +2173,18 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Bajaj Housing Finance</v>
-      </c>
-      <c r="B14" t="str">
-        <v>BAJAJ</v>
-      </c>
-      <c r="C14" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Flexi Housing Tier</v>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>106</v>
       </c>
       <c r="E14">
         <v>700</v>
@@ -1847,7 +2193,7 @@
         <v>749</v>
       </c>
       <c r="G14">
-        <v>8.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="H14">
         <v>60</v>
@@ -1862,18 +2208,18 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Bajaj Housing Finance</v>
-      </c>
-      <c r="B15" t="str">
-        <v>BAJAJ</v>
-      </c>
-      <c r="C15" t="str">
-        <v>HOME_LOAN</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Standard Housing Tier</v>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
       </c>
       <c r="E15">
         <v>680</v>
@@ -1882,7 +2228,7 @@
         <v>699</v>
       </c>
       <c r="G15">
-        <v>9.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="H15">
         <v>55</v>
@@ -1897,18 +2243,18 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Tata Capital</v>
-      </c>
-      <c r="B16" t="str">
-        <v>TATA</v>
-      </c>
-      <c r="C16" t="str">
-        <v>BUSINESS_LOAN</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Prime Business Tier</v>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>108</v>
       </c>
       <c r="E16">
         <v>750</v>
@@ -1932,18 +2278,18 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Tata Capital</v>
-      </c>
-      <c r="B17" t="str">
-        <v>TATA</v>
-      </c>
-      <c r="C17" t="str">
-        <v>BUSINESS_LOAN</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Growth Business Tier</v>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>109</v>
       </c>
       <c r="E17">
         <v>700</v>
@@ -1967,18 +2313,18 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Kotak Mahindra Bank</v>
-      </c>
-      <c r="B18" t="str">
-        <v>KOTAK</v>
-      </c>
-      <c r="C18" t="str">
-        <v>LOAN_AGAINST_PROPERTY</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Prime LAP Tier</v>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" t="s">
+        <v>110</v>
       </c>
       <c r="E18">
         <v>750</v>
@@ -2002,18 +2348,18 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Kotak Mahindra Bank</v>
-      </c>
-      <c r="B19" t="str">
-        <v>KOTAK</v>
-      </c>
-      <c r="C19" t="str">
-        <v>LOAN_AGAINST_PROPERTY</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Standard LAP Tier</v>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="s">
+        <v>111</v>
       </c>
       <c r="E19">
         <v>700</v>
@@ -2037,18 +2383,18 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Kotak Mahindra Bank</v>
-      </c>
-      <c r="B20" t="str">
-        <v>KOTAK</v>
-      </c>
-      <c r="C20" t="str">
-        <v>LOAN_AGAINST_PROPERTY</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Regular LAP Tier</v>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>112</v>
       </c>
       <c r="E20">
         <v>680</v>
@@ -2057,7 +2403,7 @@
         <v>699</v>
       </c>
       <c r="G20">
-        <v>9.95</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="H20">
         <v>50</v>
@@ -2073,8 +2419,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K20"/>
+    <ignoredError sqref="A1:K20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Quickfinsure_Bank_Policy_Cards.xlsx
+++ b/Quickfinsure_Bank_Policy_Cards.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/120435612014f931/Tài liệu/Important Sheet/Anitigravity Projects/Quickfinsure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_3F12451216A80BE399152093C815A669B06F13AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47ADCCC5-9E99-47AD-887D-B7B1C3475FAD}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_3F12451216A80BE399152093C815A669B06F13AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0F8A543-6637-4812-A91B-28125BE3C45B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bank Policies Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Eligibility &amp; Dynamic Rules" sheetId="2" r:id="rId2"/>
     <sheet name="CIBIL Rate Matrix" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CIBIL Rate Matrix'!$A$1:$K$20</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1702,6 +1705,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1858,7 +1862,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1893,7 +1897,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1928,7 +1932,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1963,7 +1967,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -1998,7 +2002,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -2033,7 +2037,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -2068,7 +2072,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -2103,7 +2107,7 @@
         <v>3500000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -2138,7 +2142,7 @@
         <v>3500000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -2173,7 +2177,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2208,7 +2212,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -2243,7 +2247,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -2278,7 +2282,7 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -2313,7 +2317,7 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -2348,7 +2352,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -2383,7 +2387,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -2419,6 +2423,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K20" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="HDFC Bank"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:K20" numberStoredAsText="1"/>
